--- a/data/gravel/Obed MMR 2025.xlsx
+++ b/data/gravel/Obed MMR 2025.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2600ADA6-393A-EE4D-9CC9-3A4184FA8CCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C09988F-D74E-8843-9928-DDAD12D5D58A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3880" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="104">
   <si>
     <t>brand</t>
   </si>
@@ -327,6 +327,24 @@
   </si>
   <si>
     <t>estimated 422</t>
+  </si>
+  <si>
+    <t>class</t>
+  </si>
+  <si>
+    <t>gravel</t>
+  </si>
+  <si>
+    <t>handlebar</t>
+  </si>
+  <si>
+    <t>drop bar</t>
+  </si>
+  <si>
+    <t>fork</t>
+  </si>
+  <si>
+    <t>rigid</t>
   </si>
 </sst>
 </file>
@@ -679,7 +697,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K71"/>
+  <dimension ref="A1:K74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1214,172 +1232,175 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>31</v>
+        <v>98</v>
       </c>
       <c r="B37" t="s">
-        <v>32</v>
+        <v>99</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>33</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>68</v>
+        <v>100</v>
+      </c>
+      <c r="B38" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>34</v>
+        <v>102</v>
+      </c>
+      <c r="B39" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>35</v>
-      </c>
-      <c r="B40">
-        <v>57</v>
+        <v>31</v>
+      </c>
+      <c r="B40" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>36</v>
-      </c>
-      <c r="B41" s="1"/>
+        <v>33</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="1">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>68</v>
+        <v>35</v>
+      </c>
+      <c r="B43">
+        <v>57</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>39</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B44" s="1"/>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45" s="1">
         <v>40</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>38</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>48</v>
-      </c>
-      <c r="B53" s="1"/>
+        <v>45</v>
+      </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>49</v>
+        <v>46</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>51</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="B56" s="1"/>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>94</v>
+      <c r="A57" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>53</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>94</v>
+        <v>50</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" t="s">
-        <v>55</v>
+      <c r="A60" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>56</v>
-      </c>
-      <c r="B61" s="1">
-        <v>2</v>
+        <v>53</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>68</v>
@@ -1387,21 +1408,20 @@
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>59</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>68</v>
+        <v>56</v>
+      </c>
+      <c r="B64" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>60</v>
-      </c>
-      <c r="B65" s="1"/>
+        <v>57</v>
+      </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>68</v>
@@ -1409,7 +1429,7 @@
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>68</v>
@@ -1417,20 +1437,21 @@
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>63</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="B68" s="1"/>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>64</v>
-      </c>
-      <c r="B69">
-        <v>3499</v>
+        <v>61</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>68</v>
@@ -1438,9 +1459,30 @@
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" t="s">
+        <v>64</v>
+      </c>
+      <c r="B72">
+        <v>3499</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" t="s">
+        <v>65</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
         <v>66</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B74" s="1" t="s">
         <v>76</v>
       </c>
     </row>

--- a/data/gravel/Obed MMR 2025.xlsx
+++ b/data/gravel/Obed MMR 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C09988F-D74E-8843-9928-DDAD12D5D58A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC0930D0-78A6-534E-9B09-D9CA2C09001B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3880" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="104">
   <si>
     <t>brand</t>
   </si>
@@ -263,9 +263,6 @@
     <t>threaded</t>
   </si>
   <si>
-    <t>us</t>
-  </si>
-  <si>
     <t>rider_min_spec</t>
   </si>
   <si>
@@ -345,6 +342,9 @@
   </si>
   <si>
     <t>rigid</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -709,7 +709,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -717,7 +717,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -741,7 +741,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -749,7 +749,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="21">
@@ -757,7 +757,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>71</v>
@@ -777,7 +777,7 @@
         <v>17</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C9" s="3">
         <v>540</v>
@@ -797,7 +797,7 @@
         <v>18</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C10" s="3">
         <v>370</v>
@@ -817,7 +817,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C11" s="3">
         <f>H11*10</f>
@@ -853,7 +853,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C12" s="3">
         <v>95</v>
@@ -873,7 +873,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C13" s="3">
         <v>430</v>
@@ -893,7 +893,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C14" s="3">
         <v>69</v>
@@ -913,7 +913,7 @@
         <v>8</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C15" s="3">
         <v>74.5</v>
@@ -933,7 +933,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C16">
         <v>440</v>
@@ -953,7 +953,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C17">
         <v>76</v>
@@ -993,7 +993,7 @@
         <v>67</v>
       </c>
       <c r="B19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C19">
         <v>606</v>
@@ -1013,7 +1013,7 @@
         <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C20">
         <v>50</v>
@@ -1033,7 +1033,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C21">
         <v>715</v>
@@ -1054,7 +1054,7 @@
         <v>24</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1181,7 +1181,7 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C33">
         <v>152</v>
@@ -1198,7 +1198,7 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C34">
         <v>163</v>
@@ -1232,26 +1232,26 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
+        <v>97</v>
+      </c>
+      <c r="B37" t="s">
         <v>98</v>
-      </c>
-      <c r="B37" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
+        <v>99</v>
+      </c>
+      <c r="B38" t="s">
         <v>100</v>
-      </c>
-      <c r="B38" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
+        <v>101</v>
+      </c>
+      <c r="B39" t="s">
         <v>102</v>
-      </c>
-      <c r="B39" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -1301,9 +1301,7 @@
       <c r="A46" t="s">
         <v>38</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>68</v>
-      </c>
+      <c r="B46" s="1"/>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
@@ -1382,7 +1380,7 @@
         <v>52</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1390,7 +1388,7 @@
         <v>53</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1483,7 +1481,7 @@
         <v>66</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Obed MMR 2025.xlsx
+++ b/data/gravel/Obed MMR 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC0930D0-78A6-534E-9B09-D9CA2C09001B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B3CAB17-2A32-1B44-B915-3DC95121EBE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3880" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="105">
   <si>
     <t>brand</t>
   </si>
@@ -345,6 +345,9 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>https://obedbikes.com/cdn/shop/files/MMR-Transparent.png?v=1753817341&amp;width=900</t>
   </si>
 </sst>
 </file>
@@ -744,6 +747,11 @@
         <v>79</v>
       </c>
     </row>
+    <row r="6" spans="1:11">
+      <c r="B6" t="s">
+        <v>104</v>
+      </c>
+    </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
         <v>5</v>

--- a/data/gravel/Obed MMR 2025.xlsx
+++ b/data/gravel/Obed MMR 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B3CAB17-2A32-1B44-B915-3DC95121EBE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9F2551A-E911-CD48-8D76-0F786E5EC22C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3880" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="107">
   <si>
     <t>brand</t>
   </si>
@@ -348,6 +348,12 @@
   </si>
   <si>
     <t>https://obedbikes.com/cdn/shop/files/MMR-Transparent.png?v=1753817341&amp;width=900</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Chattanooga, Tennessee, USA</t>
   </si>
 </sst>
 </file>
@@ -700,7 +706,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K74"/>
+  <dimension ref="A1:K75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1492,6 +1498,14 @@
         <v>103</v>
       </c>
     </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>105</v>
+      </c>
+      <c r="B75" t="s">
+        <v>106</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Obed MMR 2025.xlsx
+++ b/data/gravel/Obed MMR 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9F2551A-E911-CD48-8D76-0F786E5EC22C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E63788D-6B1C-A44C-81FD-A6B15276FD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3880" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="113">
   <si>
     <t>brand</t>
   </si>
@@ -354,6 +354,24 @@
   </si>
   <si>
     <t>Chattanooga, Tennessee, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -706,7 +724,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1339,123 +1357,110 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>43</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>75</v>
+        <v>107</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>45</v>
+        <v>109</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>46</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>68</v>
+        <v>110</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>47</v>
+        <v>111</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>48</v>
-      </c>
-      <c r="B56" s="1"/>
+        <v>112</v>
+      </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>49</v>
+        <v>43</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="1" t="s">
-        <v>52</v>
+      <c r="A60" t="s">
+        <v>46</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>53</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>93</v>
+        <v>47</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>54</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="B62" s="1"/>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>55</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>56</v>
-      </c>
-      <c r="B64" s="1">
-        <v>2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" t="s">
-        <v>58</v>
+      <c r="A66" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>60</v>
-      </c>
-      <c r="B68" s="1"/>
+        <v>54</v>
+      </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>68</v>
@@ -1463,28 +1468,28 @@
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>62</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>68</v>
+        <v>56</v>
+      </c>
+      <c r="B70" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>64</v>
-      </c>
-      <c r="B72">
-        <v>3499</v>
+        <v>58</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>68</v>
@@ -1492,17 +1497,60 @@
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>66</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>103</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="B74" s="1"/>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
+        <v>61</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>62</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>64</v>
+      </c>
+      <c r="B78">
+        <v>3499</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
+        <v>65</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
+        <v>66</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" t="s">
         <v>105</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B81" t="s">
         <v>106</v>
       </c>
     </row>
